--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260217_202615.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
